--- a/Configs/GameConfig/Datas/系统功能表.xlsx
+++ b/Configs/GameConfig/Datas/系统功能表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="14005"/>
+    <workbookView windowWidth="24500" windowHeight="16860"/>
   </bookViews>
   <sheets>
     <sheet name="主页功能" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -908,13 +908,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1204,21 +1197,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1"/>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="21.2342342342342" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5945945945946" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.2363636363636" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5909090909091" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="22.0810810810811" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.0540540540541" style="1" customWidth="1"/>
-    <col min="8" max="8" width="19.0630630630631" style="1" customWidth="1"/>
-    <col min="9" max="9" width="23.9369369369369" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.0818181818182" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.0545454545455" style="1" customWidth="1"/>
+    <col min="8" max="8" width="19.0636363636364" style="1" customWidth="1"/>
+    <col min="9" max="9" width="23.9363636363636" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.15" spans="1:11">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1250,152 +1243,137 @@
       <c r="K1" s="10"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
+      <c r="A2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>11</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B3" s="7"/>
+      <c r="C3" s="6"/>
       <c r="D3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>11</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="11"/>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
     </row>
-    <row r="5" ht="14.15" spans="1:11">
-      <c r="A5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
+    <row r="5" spans="2:3">
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="6" spans="2:3">
       <c r="B6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="B7" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="2:3">
       <c r="B8" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="2:3">
       <c r="B9" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="2:3">
       <c r="B10" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="2:3">
       <c r="B11" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3">
-      <c r="B12" s="1">
-        <v>7</v>
-      </c>
-      <c r="C12" s="1" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1410,7 +1388,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1422,7 +1400,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
